--- a/reports/rapport-tests.xlsx
+++ b/reports/rapport-tests.xlsx
@@ -3,7 +3,10 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Tests Données" sheetId="1" r:id="rId1"/>
+    <sheet name="Tests Automatiques PHPUnit" sheetId="1" r:id="rId1"/>
+    <sheet name="Fiche Hôtels" sheetId="2" r:id="rId2"/>
+    <sheet name="Calculs Tarifs" sheetId="3" r:id="rId3"/>
+    <sheet name="Stocks Chambres" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -397,14 +400,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:H76"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="38.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="60.83203125" customWidth="1"/>
-    <col min="5" max="5" width="35.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
+    <col min="4" max="4" width="55.83203125" customWidth="1"/>
+    <col min="5" max="5" width="45.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -412,6 +417,2000 @@
         <v>ID</v>
       </c>
       <c r="B1" t="str">
+        <v>Fichier / Module</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Titre du Test</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Code d'Assertion</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Résultat Attendu</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Statut</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Durée (s)</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Détail Erreur</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>AUT-1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>AuthTest.php</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Register returns token</v>
+      </c>
+      <c r="D2" t="str">
+        <v>test_register_returns_token</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Retourne HTTP 201 (Créé)</v>
+      </c>
+      <c r="F2" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G2" t="str">
+        <v>0.829</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>AUT-2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>AuthTest.php</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Login correct returns 200</v>
+      </c>
+      <c r="D3" t="str">
+        <v>test_login_correct_returns_200</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Retourne HTTP 200 (OK)</v>
+      </c>
+      <c r="F3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G3" t="str">
+        <v>0.088</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>AUT-3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AuthTest.php</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Login wrong password returns 401</v>
+      </c>
+      <c r="D4" t="str">
+        <v>test_login_wrong_password_returns_401</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Retourne HTTP 401 (Non authentifié)</v>
+      </c>
+      <c r="F4" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G4" t="str">
+        <v>0.268</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>AUT-4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>AuthTest.php</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Logout revokes token</v>
+      </c>
+      <c r="D5" t="str">
+        <v>test_logout_revokes_token</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Retourne HTTP 200 (OK)</v>
+      </c>
+      <c r="F5" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G5" t="str">
+        <v>0.044</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>AUT-5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>AvisApiTest.php</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Get avis returns list and stats</v>
+      </c>
+      <c r="D6" t="str">
+        <v>test_get_avis_returns_list_and_stats</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F6" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G6" t="str">
+        <v>0.057</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AUT-6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>AvisApiTest.php</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Post avis without token returns 401</v>
+      </c>
+      <c r="D7" t="str">
+        <v>test_post_avis_without_token_returns_401</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F7" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G7" t="str">
+        <v>0.035</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AUT-7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>AvisApiTest.php</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Post avis with token creates or updates</v>
+      </c>
+      <c r="D8" t="str">
+        <v>test_post_avis_with_token_creates_or_updates</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F8" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G8" t="str">
+        <v>0.052</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AUT-8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>AvisApiTest.php</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Post avis invalid notes returns 422</v>
+      </c>
+      <c r="D9" t="str">
+        <v>test_post_avis_invalid_notes_returns_422</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F9" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G9" t="str">
+        <v>0.053</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AUT-9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>AvisApiTest.php</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Delete avis authorized</v>
+      </c>
+      <c r="D10" t="str">
+        <v>test_delete_avis_authorized</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F10" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G10" t="str">
+        <v>0.044</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AUT-10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>ChambreApiTest.php</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Get chambres returns list</v>
+      </c>
+      <c r="D11" t="str">
+        <v>test_get_chambres_returns_list</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G11" t="str">
+        <v>0.050</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>AUT-11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>ChambreApiTest.php</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Get chambre inexistante returns 404</v>
+      </c>
+      <c r="D12" t="str">
+        <v>test_get_chambre_inexistante_returns_404</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Retourne HTTP 404 (Introuvable)</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G12" t="str">
+        <v>0.038</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>AUT-12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>ChambreApiTest.php</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Create chambre without token returns 401</v>
+      </c>
+      <c r="D13" t="str">
+        <v>test_create_chambre_without_token_returns_401</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G13" t="str">
+        <v>0.037</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>AUT-13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>ChambreApiTest.php</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Create chambre valid returns 201</v>
+      </c>
+      <c r="D14" t="str">
+        <v>test_create_chambre_valid_returns_201</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G14" t="str">
+        <v>0.040</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>AUT-14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>ChambreApiTest.php</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Update chambre prix returns 200</v>
+      </c>
+      <c r="D15" t="str">
+        <v>test_update_chambre_prix_returns_200</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G15" t="str">
+        <v>0.045</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>AUT-15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>ChambreApiTest.php</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Delete chambre returns 200</v>
+      </c>
+      <c r="D16" t="str">
+        <v>test_delete_chambre_returns_200</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F16" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G16" t="str">
+        <v>0.040</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>AUT-16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>ExampleTest.php</v>
+      </c>
+      <c r="C17" t="str">
+        <v>The application returns a successful response</v>
+      </c>
+      <c r="D17" t="str">
+        <v>test_the_application_returns_a_successful_response</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Retourne HTTP 200 (OK)</v>
+      </c>
+      <c r="F17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G17" t="str">
+        <v>0.071</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>AUT-17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>HotelApiTest.php</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Get hotels returns list</v>
+      </c>
+      <c r="D18" t="str">
+        <v>test_get_hotels_returns_list</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Retourne HTTP 200 (OK)</v>
+      </c>
+      <c r="F18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G18" t="str">
+        <v>0.089</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>AUT-18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>HotelApiTest.php</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Get hotel by id returns correct hotel</v>
+      </c>
+      <c r="D19" t="str">
+        <v>test_get_hotel_by_id_returns_correct_hotel</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G19" t="str">
+        <v>0.104</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>AUT-19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>HotelApiTest.php</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Get hotel inexistant returns 404</v>
+      </c>
+      <c r="D20" t="str">
+        <v>test_get_hotel_inexistant_returns_404</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Retourne HTTP 404 (Introuvable)</v>
+      </c>
+      <c r="F20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G20" t="str">
+        <v>0.034</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>AUT-20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>HotelApiTest.php</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Create hotel without token returns 401</v>
+      </c>
+      <c r="D21" t="str">
+        <v>test_create_hotel_without_token_returns_401</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Retourne HTTP 401 (Non authentifié)</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G21" t="str">
+        <v>0.033</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>AUT-21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>HotelApiTest.php</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Create hotel with token returns 201</v>
+      </c>
+      <c r="D22" t="str">
+        <v>test_create_hotel_with_token_returns_201</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Retourne HTTP 201 (Créé)</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G22" t="str">
+        <v>0.073</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>AUT-22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>ProfilApiTest.php</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Me returns authenticated user</v>
+      </c>
+      <c r="D23" t="str">
+        <v>test_me_returns_authenticated_user</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Retourne HTTP 200 (OK)</v>
+      </c>
+      <c r="F23" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G23" t="str">
+        <v>0.081</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>AUT-23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>ProfilApiTest.php</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Update profile updates correctly</v>
+      </c>
+      <c r="D24" t="str">
+        <v>test_update_profile_updates_correctly</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Retourne HTTP 200 (OK)</v>
+      </c>
+      <c r="F24" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G24" t="str">
+        <v>0.039</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>AUT-24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>ProfilApiTest.php</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Update password wrong current returns 422</v>
+      </c>
+      <c r="D25" t="str">
+        <v>test_update_password_wrong_current_returns_422</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Retourne HTTP 422 (Erreur validation)</v>
+      </c>
+      <c r="F25" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G25" t="str">
+        <v>0.042</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>AUT-25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>ReservationAdminTest.php</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Get all reservations without admin returns 401</v>
+      </c>
+      <c r="D26" t="str">
+        <v>test_get_all_reservations_without_admin_returns_401</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Retourne HTTP 403 (Interdit)</v>
+      </c>
+      <c r="F26" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G26" t="str">
+        <v>0.075</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>AUT-26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>ReservationAdminTest.php</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Admin can list all reservations</v>
+      </c>
+      <c r="D27" t="str">
+        <v>test_admin_can_list_all_reservations</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Retourne HTTP 200 (OK)</v>
+      </c>
+      <c r="F27" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G27" t="str">
+        <v>0.048</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>AUT-27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>ReservationAdminTest.php</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Admin can confirm reservation</v>
+      </c>
+      <c r="D28" t="str">
+        <v>test_admin_can_confirm_reservation</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F28" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G28" t="str">
+        <v>0.042</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>AUT-28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>ReservationAdminTest.php</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Admin can cancel reservation</v>
+      </c>
+      <c r="D29" t="str">
+        <v>test_admin_can_cancel_reservation</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F29" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G29" t="str">
+        <v>0.042</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>AUT-29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>ReservationAdminTest.php</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Admin update invalid statut returns 422</v>
+      </c>
+      <c r="D30" t="str">
+        <v>test_admin_update_invalid_statut_returns_422</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F30" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G30" t="str">
+        <v>0.048</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>AUT-30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>ReservationAdminTest.php</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Admin can delete reservation</v>
+      </c>
+      <c r="D31" t="str">
+        <v>test_admin_can_delete_reservation</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G31" t="str">
+        <v>0.038</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>AUT-31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>ReservationApiTest.php</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Create reservation without token returns 401</v>
+      </c>
+      <c r="D32" t="str">
+        <v>test_create_reservation_without_token_returns_401</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Retourne HTTP 401 (Non authentifié)</v>
+      </c>
+      <c r="F32" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G32" t="str">
+        <v>0.041</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>AUT-32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>ReservationApiTest.php</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Create reservation with invalid data returns 422</v>
+      </c>
+      <c r="D33" t="str">
+        <v>test_create_reservation_with_invalid_data_returns_422</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Retourne HTTP 422 (Erreur validation)</v>
+      </c>
+      <c r="F33" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G33" t="str">
+        <v>0.070</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>AUT-33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>ReservationApiTest.php</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Create reservation valid returns 201 with prix</v>
+      </c>
+      <c r="D34" t="str">
+        <v>test_create_reservation_valid_returns_201_with_prix</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Retourne HTTP 201 (Créé)</v>
+      </c>
+      <c r="F34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G34" t="str">
+        <v>0.046</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>AUT-34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>ReservationApiTest.php</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Create reservation chambre wrong hotel returns 422</v>
+      </c>
+      <c r="D35" t="str">
+        <v>test_create_reservation_chambre_wrong_hotel_returns_422</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G35" t="str">
+        <v>0.045</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>AUT-35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>ReservationApiTest.php</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Create reservation capacite insuffisante returns 422</v>
+      </c>
+      <c r="D36" t="str">
+        <v>test_create_reservation_capacite_insuffisante_returns_422</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Retourne HTTP 422 (Erreur validation)</v>
+      </c>
+      <c r="F36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G36" t="str">
+        <v>0.039</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>AUT-36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>DestinationTest.php</v>
+      </c>
+      <c r="C37" t="str">
+        <v>HasNom retourne true si nom renseigne</v>
+      </c>
+      <c r="D37" t="str">
+        <v>test_hasNom_retourne_true_si_nom_renseigne</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G37" t="str">
+        <v>0.039</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>AUT-37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>DestinationTest.php</v>
+      </c>
+      <c r="C38" t="str">
+        <v>HasNom retourne false si nom vide</v>
+      </c>
+      <c r="D38" t="str">
+        <v>test_hasNom_retourne_false_si_nom_vide</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G38" t="str">
+        <v>0.001</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>AUT-38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>DestinationTest.php</v>
+      </c>
+      <c r="C39" t="str">
+        <v>HasNom retourne false si nom manquant</v>
+      </c>
+      <c r="D39" t="str">
+        <v>test_hasNom_retourne_false_si_nom_manquant</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G39" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>AUT-39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>DestinationTest.php</v>
+      </c>
+      <c r="C40" t="str">
+        <v>HasRegion retourne true si region renseignee</v>
+      </c>
+      <c r="D40" t="str">
+        <v>test_hasRegion_retourne_true_si_region_renseignee</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G40" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>AUT-40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>DestinationTest.php</v>
+      </c>
+      <c r="C41" t="str">
+        <v>HasRegion retourne false si region vide</v>
+      </c>
+      <c r="D41" t="str">
+        <v>test_hasRegion_retourne_false_si_region_vide</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G41" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>AUT-41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>DestinationTest.php</v>
+      </c>
+      <c r="C42" t="str">
+        <v>GetNomComplet retourne format correct</v>
+      </c>
+      <c r="D42" t="str">
+        <v>test_getNomComplet_retourne_format_correct</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G42" t="str">
+        <v>0.001</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>AUT-42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>ExampleTest.php</v>
+      </c>
+      <c r="C43" t="str">
+        <v>That true is true</v>
+      </c>
+      <c r="D43" t="str">
+        <v>test_that_true_is_true</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G43" t="str">
+        <v>0.034</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>AUT-43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>HotelTest.php</v>
+      </c>
+      <c r="C44" t="str">
+        <v>IsDisponible retourne true quand disponible</v>
+      </c>
+      <c r="D44" t="str">
+        <v>test_isDisponible_retourne_true_quand_disponible</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G44" t="str">
+        <v>0.003</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>AUT-44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>HotelTest.php</v>
+      </c>
+      <c r="C45" t="str">
+        <v>IsDisponible retourne false quand indisponible</v>
+      </c>
+      <c r="D45" t="str">
+        <v>test_isDisponible_retourne_false_quand_indisponible</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G45" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>AUT-45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>HotelTest.php</v>
+      </c>
+      <c r="C46" t="str">
+        <v>IsEtoilesValide retourne true pour 1 a 5</v>
+      </c>
+      <c r="D46" t="str">
+        <v>test_isEtoilesValide_retourne_true_pour_1_a_5</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F46" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G46" t="str">
+        <v>0.001</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>AUT-46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>HotelTest.php</v>
+      </c>
+      <c r="C47" t="str">
+        <v>IsEtoilesValide retourne false pour zero</v>
+      </c>
+      <c r="D47" t="str">
+        <v>test_isEtoilesValide_retourne_false_pour_zero</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G47" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>AUT-47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>HotelTest.php</v>
+      </c>
+      <c r="C48" t="str">
+        <v>IsEtoilesValide retourne false pour six</v>
+      </c>
+      <c r="D48" t="str">
+        <v>test_isEtoilesValide_retourne_false_pour_six</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G48" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>AUT-48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>HotelTest.php</v>
+      </c>
+      <c r="C49" t="str">
+        <v>IsPrixValide retourne true pour prix positif</v>
+      </c>
+      <c r="D49" t="str">
+        <v>test_isPrixValide_retourne_true_pour_prix_positif</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F49" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G49" t="str">
+        <v>0.015</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>AUT-49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>HotelTest.php</v>
+      </c>
+      <c r="C50" t="str">
+        <v>IsPrixValide retourne false pour prix zero</v>
+      </c>
+      <c r="D50" t="str">
+        <v>test_isPrixValide_retourne_false_pour_prix_zero</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F50" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G50" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>AUT-50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>HotelTest.php</v>
+      </c>
+      <c r="C51" t="str">
+        <v>IsPrixValide retourne false pour prix negatif</v>
+      </c>
+      <c r="D51" t="str">
+        <v>test_isPrixValide_retourne_false_pour_prix_negatif</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F51" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G51" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>AUT-51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C52" t="str">
+        <v>GetNbNuits retourne nombre correct</v>
+      </c>
+      <c r="D52" t="str">
+        <v>test_getNbNuits_retourne_nombre_correct</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F52" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G52" t="str">
+        <v>0.010</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>AUT-52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C53" t="str">
+        <v>GetNbNuits retourne zero si meme date</v>
+      </c>
+      <c r="D53" t="str">
+        <v>test_getNbNuits_retourne_zero_si_meme_date</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F53" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G53" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>AUT-53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C54" t="str">
+        <v>GetNbNuits retourne zero si depart avant arrivee</v>
+      </c>
+      <c r="D54" t="str">
+        <v>test_getNbNuits_retourne_zero_si_depart_avant_arrivee</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F54" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G54" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>AUT-54</v>
+      </c>
+      <c r="B55" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C55" t="str">
+        <v>GetNbNuits retourne zero si dates manquantes</v>
+      </c>
+      <c r="D55" t="str">
+        <v>test_getNbNuits_retourne_zero_si_dates_manquantes</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F55" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G55" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>AUT-55</v>
+      </c>
+      <c r="B56" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C56" t="str">
+        <v>CalculatePrixTotal correct sans enfants</v>
+      </c>
+      <c r="D56" t="str">
+        <v>test_calculatePrixTotal_correct_sans_enfants</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F56" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G56" t="str">
+        <v>0.001</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>AUT-56</v>
+      </c>
+      <c r="B57" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C57" t="str">
+        <v>CalculatePrixTotal avec enfants de differents ages</v>
+      </c>
+      <c r="D57" t="str">
+        <v>test_calculatePrixTotal_avec_enfants_de_differents_ages</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F57" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G57" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>AUT-57</v>
+      </c>
+      <c r="B58" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C58" t="str">
+        <v>CalculatePrixTotal une nuit une chambre sans enfants</v>
+      </c>
+      <c r="D58" t="str">
+        <v>test_calculatePrixTotal_une_nuit_une_chambre_sans_enfants</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F58" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G58" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>AUT-58</v>
+      </c>
+      <c r="B59" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C59" t="str">
+        <v>CalculatePrixTotal zero si meme date</v>
+      </c>
+      <c r="D59" t="str">
+        <v>test_calculatePrixTotal_zero_si_meme_date</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F59" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G59" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>AUT-59</v>
+      </c>
+      <c r="B60" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C60" t="str">
+        <v>IsStatutValide retourne true pour en attente</v>
+      </c>
+      <c r="D60" t="str">
+        <v>test_isStatutValide_retourne_true_pour_en_attente</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F60" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G60" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>AUT-60</v>
+      </c>
+      <c r="B61" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C61" t="str">
+        <v>IsStatutValide retourne true pour confirmee</v>
+      </c>
+      <c r="D61" t="str">
+        <v>test_isStatutValide_retourne_true_pour_confirmee</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F61" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G61" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>AUT-61</v>
+      </c>
+      <c r="B62" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C62" t="str">
+        <v>IsStatutValide retourne true pour annulee</v>
+      </c>
+      <c r="D62" t="str">
+        <v>test_isStatutValide_retourne_true_pour_annulee</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F62" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G62" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>AUT-62</v>
+      </c>
+      <c r="B63" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C63" t="str">
+        <v>IsStatutValide retourne false pour statut inconnu</v>
+      </c>
+      <c r="D63" t="str">
+        <v>test_isStatutValide_retourne_false_pour_statut_inconnu</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F63" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G63" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>AUT-63</v>
+      </c>
+      <c r="B64" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C64" t="str">
+        <v>CanTransitionTo en attente vers confirmee</v>
+      </c>
+      <c r="D64" t="str">
+        <v>test_canTransitionTo_en_attente_vers_confirmee</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F64" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G64" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>AUT-64</v>
+      </c>
+      <c r="B65" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C65" t="str">
+        <v>CanTransitionTo en attente vers annulee</v>
+      </c>
+      <c r="D65" t="str">
+        <v>test_canTransitionTo_en_attente_vers_annulee</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F65" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G65" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>AUT-65</v>
+      </c>
+      <c r="B66" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C66" t="str">
+        <v>CanTransitionTo annulee est etat terminal</v>
+      </c>
+      <c r="D66" t="str">
+        <v>test_canTransitionTo_annulee_est_etat_terminal</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F66" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G66" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>AUT-66</v>
+      </c>
+      <c r="B67" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C67" t="str">
+        <v>CanTransitionTo retourne false pour statut invalide</v>
+      </c>
+      <c r="D67" t="str">
+        <v>test_canTransitionTo_retourne_false_pour_statut_invalide</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F67" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G67" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>AUT-67</v>
+      </c>
+      <c r="B68" t="str">
+        <v>ReservationTest.php</v>
+      </c>
+      <c r="C68" t="str">
+        <v>GetStatutsValides contient les trois statuts</v>
+      </c>
+      <c r="D68" t="str">
+        <v>test_getStatutsValides_contient_les_trois_statuts</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F68" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G68" t="str">
+        <v>0.005</v>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>AUT-68</v>
+      </c>
+      <c r="B69" t="str">
+        <v>VoyageTest.php</v>
+      </c>
+      <c r="C69" t="str">
+        <v>IsPrixValide retourne true pour prix positif</v>
+      </c>
+      <c r="D69" t="str">
+        <v>test_isPrixValide_retourne_true_pour_prix_positif</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F69" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G69" t="str">
+        <v>0.015</v>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>AUT-69</v>
+      </c>
+      <c r="B70" t="str">
+        <v>VoyageTest.php</v>
+      </c>
+      <c r="C70" t="str">
+        <v>IsPrixValide retourne false pour prix zero</v>
+      </c>
+      <c r="D70" t="str">
+        <v>test_isPrixValide_retourne_false_pour_prix_zero</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F70" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G70" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>AUT-70</v>
+      </c>
+      <c r="B71" t="str">
+        <v>VoyageTest.php</v>
+      </c>
+      <c r="C71" t="str">
+        <v>IsPrixValide retourne false pour prix negatif</v>
+      </c>
+      <c r="D71" t="str">
+        <v>test_isPrixValide_retourne_false_pour_prix_negatif</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F71" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G71" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>AUT-71</v>
+      </c>
+      <c r="B72" t="str">
+        <v>VoyageTest.php</v>
+      </c>
+      <c r="C72" t="str">
+        <v>IsDureeValide retourne true pour un jour</v>
+      </c>
+      <c r="D72" t="str">
+        <v>test_isDureeValide_retourne_true_pour_un_jour</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F72" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G72" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>AUT-72</v>
+      </c>
+      <c r="B73" t="str">
+        <v>VoyageTest.php</v>
+      </c>
+      <c r="C73" t="str">
+        <v>IsDureeValide retourne true pour une semaine</v>
+      </c>
+      <c r="D73" t="str">
+        <v>test_isDureeValide_retourne_true_pour_une_semaine</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F73" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G73" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>AUT-73</v>
+      </c>
+      <c r="B74" t="str">
+        <v>VoyageTest.php</v>
+      </c>
+      <c r="C74" t="str">
+        <v>IsDureeValide retourne false pour zero jour</v>
+      </c>
+      <c r="D74" t="str">
+        <v>test_isDureeValide_retourne_false_pour_zero_jour</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F74" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G74" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>AUT-74</v>
+      </c>
+      <c r="B75" t="str">
+        <v>VoyageTest.php</v>
+      </c>
+      <c r="C75" t="str">
+        <v>GetDureeLabel retourne un jour au singulier</v>
+      </c>
+      <c r="D75" t="str">
+        <v>test_getDureeLabel_retourne_un_jour_au_singulier</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F75" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G75" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>AUT-75</v>
+      </c>
+      <c r="B76" t="str">
+        <v>VoyageTest.php</v>
+      </c>
+      <c r="C76" t="str">
+        <v>GetDureeLabel retourne pluriel pour plusieurs jours</v>
+      </c>
+      <c r="D76" t="str">
+        <v>test_getDureeLabel_retourne_pluriel_pour_plusieurs_jours</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Exécution correcte</v>
+      </c>
+      <c r="F76" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G76" t="str">
+        <v>0.000</v>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H76"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E6"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
         <v>Nom Hôtel</v>
       </c>
       <c r="C1" t="str">
@@ -421,9 +2420,6 @@
         <v>Description</v>
       </c>
       <c r="E1" t="str">
-        <v>Résultat Attendu</v>
-      </c>
-      <c r="F1" t="str">
         <v>Statut</v>
       </c>
     </row>
@@ -441,9 +2437,6 @@
         <v>Yasmine Hammamet, cet hôtel propose un hébergement confortable</v>
       </c>
       <c r="E2" t="str">
-        <v>Doit correspondre exactement en base</v>
-      </c>
-      <c r="F2" t="str">
         <v>PASS</v>
       </c>
     </row>
@@ -461,9 +2454,6 @@
         <v>entouré de jardins d'orangers avec un accès direct à une plage privée</v>
       </c>
       <c r="E3" t="str">
-        <v>Doit correspondre exactement en base</v>
-      </c>
-      <c r="F3" t="str">
         <v>PASS</v>
       </c>
     </row>
@@ -481,9 +2471,6 @@
         <v>Sidi Mehrez, réputé pour son centre de thalassothérapie</v>
       </c>
       <c r="E4" t="str">
-        <v>Doit correspondre exactement en base</v>
-      </c>
-      <c r="F4" t="str">
         <v>PASS</v>
       </c>
     </row>
@@ -501,9 +2488,6 @@
         <v>architecture traditionnelle djerbienne et confort moderne</v>
       </c>
       <c r="E5" t="str">
-        <v>Doit correspondre exactement en base</v>
-      </c>
-      <c r="F5" t="str">
         <v>PASS</v>
       </c>
     </row>
@@ -521,15 +2505,307 @@
         <v>centre de Sousse, avec une plage de sable fin privée</v>
       </c>
       <c r="E6" t="str">
-        <v>Doit correspondre exactement en base</v>
-      </c>
-      <c r="F6" t="str">
         <v>PASS</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Nom Hôtel</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Chambre</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Pension</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Nuits</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Ages Enfants</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Prix Attendu</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Statut</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Prix Réel</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>C-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>El Mouradi El Menzah</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Chambre Single Standard</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Petit Déjeuner</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2">
+        <v>96</v>
+      </c>
+      <c r="H2" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>C-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>El Mouradi El Menzah</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Chambre Single Standard</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Demi Pension</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3">
+        <v>408</v>
+      </c>
+      <c r="H3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I3">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>C-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>El Mouradi El Menzah</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Chambre Double Standard</v>
+      </c>
+      <c r="D4" t="str">
+        <v>All Inclusive</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="str">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>540</v>
+      </c>
+      <c r="H4" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I4">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>C-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>El Mouradi El Menzah</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Chambre Double Standard</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Petit Déjeuner</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="str">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>300</v>
+      </c>
+      <c r="H5" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I5">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>C-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>El Mouradi El Menzah</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Chambre Double Standard</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Petit Déjeuner</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="str">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>240</v>
+      </c>
+      <c r="H6" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I6">
+        <v>240</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Nom Hôtel</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Chambre</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Quantité Attendue</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Statut</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Quantité Réelle</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Q-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>El Mouradi El Menzah</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Chambre Single Standard</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Q-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>El Mouradi El Menzah</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Chambre Single Vue Piscine</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Q-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>The Orangers Garden Villa &amp; Bungalows</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Chambre Double Standard</v>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F4">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/rapport-tests.xlsx
+++ b/reports/rapport-tests.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C351F2-B92E-425C-B320-C7581DDB0D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Hôtels" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Chambres" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Pensions" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Destination" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Example" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Hotel" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Reservation" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Voyage" state="visible" r:id="rId11"/>
+    <sheet name="Hôtels" sheetId="1" r:id="rId1"/>
+    <sheet name="Chambres" sheetId="2" r:id="rId2"/>
+    <sheet name="Pensions" sheetId="3" r:id="rId3"/>
+    <sheet name="Destination" sheetId="4" r:id="rId4"/>
+    <sheet name="Example" sheetId="5" r:id="rId5"/>
+    <sheet name="Hotel" sheetId="6" r:id="rId6"/>
+    <sheet name="Reservation" sheetId="7" r:id="rId7"/>
+    <sheet name="Voyage" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -449,18 +454,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
@@ -835,14 +842,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="18" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="116.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -862,7 +874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -882,7 +894,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -902,7 +914,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -922,7 +934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -942,7 +954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -964,19 +976,25 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="7" width="18" customWidth="1"/>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -999,7 +1017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1022,7 +1040,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1045,7 +1063,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1068,7 +1086,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1091,7 +1109,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1114,7 +1132,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1137,7 +1155,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1160,7 +1178,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1183,7 +1201,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1206,7 +1224,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1229,7 +1247,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1252,7 +1270,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1275,7 +1293,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1298,7 +1316,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1321,7 +1339,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1344,7 +1362,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1367,7 +1385,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1390,7 +1408,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1413,7 +1431,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1436,7 +1454,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1459,7 +1477,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1482,7 +1500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1505,7 +1523,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1528,7 +1546,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1551,7 +1569,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1574,7 +1592,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1597,7 +1615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1620,7 +1638,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1643,7 +1661,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1666,7 +1684,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1689,7 +1707,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1712,7 +1730,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1735,7 +1753,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1758,7 +1776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1781,7 +1799,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1804,7 +1822,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1827,7 +1845,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1850,7 +1868,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1873,7 +1891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1896,7 +1914,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1919,7 +1937,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1942,7 +1960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1965,7 +1983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1988,7 +2006,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2011,7 +2029,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2034,7 +2052,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2057,7 +2075,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2080,7 +2098,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2103,7 +2121,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2128,19 +2146,25 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G196"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="7" width="18" customWidth="1"/>
+    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2163,7 +2187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2186,7 +2210,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2209,7 +2233,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2232,7 +2256,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2255,7 +2279,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2278,7 +2302,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2301,7 +2325,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2324,7 +2348,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2347,7 +2371,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2370,7 +2394,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2393,7 +2417,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2416,7 +2440,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2439,7 +2463,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2462,7 +2486,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2485,7 +2509,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2508,7 +2532,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2531,7 +2555,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2554,7 +2578,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2577,7 +2601,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2600,7 +2624,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2623,7 +2647,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2646,7 +2670,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2669,7 +2693,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2692,7 +2716,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2715,7 +2739,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2738,7 +2762,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2761,7 +2785,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2784,7 +2808,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2807,7 +2831,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2830,7 +2854,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2853,7 +2877,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2876,7 +2900,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2899,7 +2923,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2922,7 +2946,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2945,7 +2969,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2968,7 +2992,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2991,7 +3015,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3014,7 +3038,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3037,7 +3061,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3060,7 +3084,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3083,7 +3107,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3106,7 +3130,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3129,7 +3153,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3152,7 +3176,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3175,7 +3199,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3198,7 +3222,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3221,7 +3245,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3244,7 +3268,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3267,7 +3291,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3290,7 +3314,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3313,7 +3337,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3336,7 +3360,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3359,7 +3383,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3382,7 +3406,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3405,7 +3429,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3428,7 +3452,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3451,7 +3475,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3474,7 +3498,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3497,7 +3521,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3520,7 +3544,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3543,7 +3567,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3566,7 +3590,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3589,7 +3613,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3612,7 +3636,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3635,7 +3659,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3658,7 +3682,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3681,7 +3705,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3704,7 +3728,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3727,7 +3751,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3750,7 +3774,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3773,7 +3797,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3796,7 +3820,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3819,7 +3843,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3842,7 +3866,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3865,7 +3889,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3888,7 +3912,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3911,7 +3935,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3934,7 +3958,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3957,7 +3981,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3980,7 +4004,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4003,7 +4027,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4026,7 +4050,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4049,7 +4073,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4072,7 +4096,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4095,7 +4119,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4118,7 +4142,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4141,7 +4165,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4164,7 +4188,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4187,7 +4211,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -4210,7 +4234,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -4233,7 +4257,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -4256,7 +4280,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -4279,7 +4303,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -4302,7 +4326,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -4325,7 +4349,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4348,7 +4372,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -4371,7 +4395,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -4394,7 +4418,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -4417,7 +4441,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4440,7 +4464,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -4463,7 +4487,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -4486,7 +4510,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -4509,7 +4533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -4532,7 +4556,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -4555,7 +4579,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -4578,7 +4602,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -4601,7 +4625,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -4624,7 +4648,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -4647,7 +4671,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -4670,7 +4694,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -4693,7 +4717,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -4716,7 +4740,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -4739,7 +4763,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -4762,7 +4786,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -4785,7 +4809,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -4808,7 +4832,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -4831,7 +4855,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -4854,7 +4878,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -4877,7 +4901,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -4900,7 +4924,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -4923,7 +4947,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -4946,7 +4970,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -4969,7 +4993,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -4992,7 +5016,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -5015,7 +5039,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -5038,7 +5062,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -5061,7 +5085,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -5084,7 +5108,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -5107,7 +5131,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -5130,7 +5154,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -5153,7 +5177,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -5176,7 +5200,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -5199,7 +5223,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -5222,7 +5246,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -5245,7 +5269,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -5268,7 +5292,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -5291,7 +5315,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -5314,7 +5338,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -5337,7 +5361,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -5360,7 +5384,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -5383,7 +5407,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -5406,7 +5430,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -5429,7 +5453,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -5452,7 +5476,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -5475,7 +5499,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -5498,7 +5522,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -5521,7 +5545,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -5544,7 +5568,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -5567,7 +5591,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -5590,7 +5614,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -5613,7 +5637,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -5636,7 +5660,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -5659,7 +5683,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -5682,7 +5706,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -5705,7 +5729,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -5728,7 +5752,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -5751,7 +5775,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -5774,7 +5798,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -5797,7 +5821,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -5820,7 +5844,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -5843,7 +5867,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -5866,7 +5890,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -5889,7 +5913,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -5912,7 +5936,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -5935,7 +5959,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -5958,7 +5982,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -5981,7 +6005,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -6004,7 +6028,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -6027,7 +6051,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -6050,7 +6074,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -6073,7 +6097,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -6096,7 +6120,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -6119,7 +6143,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -6142,7 +6166,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -6165,7 +6189,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -6188,7 +6212,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -6211,7 +6235,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -6234,7 +6258,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -6257,7 +6281,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -6280,7 +6304,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -6303,7 +6327,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -6326,7 +6350,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -6349,7 +6373,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -6372,7 +6396,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -6395,7 +6419,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -6418,7 +6442,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -6441,7 +6465,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -6464,7 +6488,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -6487,7 +6511,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -6510,7 +6534,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -6533,7 +6557,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -6556,7 +6580,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -6579,7 +6603,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -6602,7 +6626,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -6625,7 +6649,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -6650,19 +6674,26 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="18" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6688,7 +6719,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6708,13 +6739,13 @@
         <v>56</v>
       </c>
       <c r="G2">
-        <v>0.028516</v>
+        <v>2.8516E-2</v>
       </c>
       <c r="H2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6734,13 +6765,13 @@
         <v>56</v>
       </c>
       <c r="G3">
-        <v>0.000488</v>
+        <v>4.8799999999999999E-4</v>
       </c>
       <c r="H3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6760,13 +6791,13 @@
         <v>56</v>
       </c>
       <c r="G4">
-        <v>0.000223</v>
+        <v>2.23E-4</v>
       </c>
       <c r="H4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6786,13 +6817,13 @@
         <v>56</v>
       </c>
       <c r="G5">
-        <v>0.000181</v>
+        <v>1.8100000000000001E-4</v>
       </c>
       <c r="H5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6812,13 +6843,13 @@
         <v>56</v>
       </c>
       <c r="G6">
-        <v>0.000128</v>
+        <v>1.2799999999999999E-4</v>
       </c>
       <c r="H6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6838,7 +6869,7 @@
         <v>56</v>
       </c>
       <c r="G7">
-        <v>0.000667</v>
+        <v>6.6699999999999995E-4</v>
       </c>
       <c r="H7" t="s">
         <v>57</v>
@@ -6846,19 +6877,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="18" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6878,7 +6914,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6892,7 +6928,7 @@
         <v>56</v>
       </c>
       <c r="E2">
-        <v>0.000131</v>
+        <v>1.3100000000000001E-4</v>
       </c>
       <c r="F2" t="s">
         <v>57</v>
@@ -6900,19 +6936,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="9" width="18" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6941,7 +6985,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6964,13 +7008,13 @@
         <v>56</v>
       </c>
       <c r="H2">
-        <v>0.000799</v>
+        <v>7.9900000000000001E-4</v>
       </c>
       <c r="I2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6993,13 +7037,13 @@
         <v>56</v>
       </c>
       <c r="H3">
-        <v>0.000151</v>
+        <v>1.5100000000000001E-4</v>
       </c>
       <c r="I3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7022,13 +7066,13 @@
         <v>56</v>
       </c>
       <c r="H4">
-        <v>0.000234</v>
+        <v>2.34E-4</v>
       </c>
       <c r="I4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -7051,13 +7095,13 @@
         <v>56</v>
       </c>
       <c r="H5">
-        <v>0.000119</v>
+        <v>1.1900000000000001E-4</v>
       </c>
       <c r="I5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -7080,13 +7124,13 @@
         <v>56</v>
       </c>
       <c r="H6">
-        <v>0.000119</v>
+        <v>1.1900000000000001E-4</v>
       </c>
       <c r="I6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -7109,13 +7153,13 @@
         <v>56</v>
       </c>
       <c r="H7">
-        <v>0.000141</v>
+        <v>1.4100000000000001E-4</v>
       </c>
       <c r="I7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -7138,13 +7182,13 @@
         <v>56</v>
       </c>
       <c r="H8">
-        <v>0.000122</v>
+        <v>1.22E-4</v>
       </c>
       <c r="I8" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7167,7 +7211,7 @@
         <v>56</v>
       </c>
       <c r="H9">
-        <v>0.000114</v>
+        <v>1.1400000000000001E-4</v>
       </c>
       <c r="I9" t="s">
         <v>57</v>
@@ -7175,19 +7219,29 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="11" width="18" customWidth="1"/>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7222,7 +7276,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7251,13 +7305,13 @@
         <v>56</v>
       </c>
       <c r="J2">
-        <v>0.000778</v>
+        <v>7.7800000000000005E-4</v>
       </c>
       <c r="K2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7286,13 +7340,13 @@
         <v>56</v>
       </c>
       <c r="J3">
-        <v>0.000167</v>
+        <v>1.6699999999999999E-4</v>
       </c>
       <c r="K3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7321,13 +7375,13 @@
         <v>56</v>
       </c>
       <c r="J4">
-        <v>0.000166</v>
+        <v>1.66E-4</v>
       </c>
       <c r="K4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -7356,13 +7410,13 @@
         <v>56</v>
       </c>
       <c r="J5">
-        <v>0.000145</v>
+        <v>1.45E-4</v>
       </c>
       <c r="K5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -7391,13 +7445,13 @@
         <v>56</v>
       </c>
       <c r="J6">
-        <v>0.000644</v>
+        <v>6.4400000000000004E-4</v>
       </c>
       <c r="K6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -7426,13 +7480,13 @@
         <v>56</v>
       </c>
       <c r="J7">
-        <v>0.000224</v>
+        <v>2.24E-4</v>
       </c>
       <c r="K7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -7461,13 +7515,13 @@
         <v>56</v>
       </c>
       <c r="J8">
-        <v>0.000169</v>
+        <v>1.6899999999999999E-4</v>
       </c>
       <c r="K8" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7496,13 +7550,13 @@
         <v>56</v>
       </c>
       <c r="J9">
-        <v>0.000174</v>
+        <v>1.74E-4</v>
       </c>
       <c r="K9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -7531,13 +7585,13 @@
         <v>56</v>
       </c>
       <c r="J10">
-        <v>0.00014</v>
+        <v>1.3999999999999999E-4</v>
       </c>
       <c r="K10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -7566,13 +7620,13 @@
         <v>56</v>
       </c>
       <c r="J11">
-        <v>0.000112</v>
+        <v>1.12E-4</v>
       </c>
       <c r="K11" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -7601,13 +7655,13 @@
         <v>56</v>
       </c>
       <c r="J12">
-        <v>0.000121</v>
+        <v>1.21E-4</v>
       </c>
       <c r="K12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -7636,13 +7690,13 @@
         <v>56</v>
       </c>
       <c r="J13">
-        <v>0.000132</v>
+        <v>1.3200000000000001E-4</v>
       </c>
       <c r="K13" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -7671,13 +7725,13 @@
         <v>56</v>
       </c>
       <c r="J14">
-        <v>0.000136</v>
+        <v>1.36E-4</v>
       </c>
       <c r="K14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -7706,13 +7760,13 @@
         <v>56</v>
       </c>
       <c r="J15">
-        <v>0.000117</v>
+        <v>1.17E-4</v>
       </c>
       <c r="K15" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -7741,13 +7795,13 @@
         <v>56</v>
       </c>
       <c r="J16">
-        <v>0.000132</v>
+        <v>1.3200000000000001E-4</v>
       </c>
       <c r="K16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -7776,13 +7830,13 @@
         <v>56</v>
       </c>
       <c r="J17">
-        <v>0.000108</v>
+        <v>1.08E-4</v>
       </c>
       <c r="K17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -7811,7 +7865,7 @@
         <v>56</v>
       </c>
       <c r="J18">
-        <v>0.00161</v>
+        <v>1.6100000000000001E-3</v>
       </c>
       <c r="K18" t="s">
         <v>57</v>
@@ -7819,19 +7873,26 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="18" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7857,7 +7918,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7877,13 +7938,13 @@
         <v>56</v>
       </c>
       <c r="G2">
-        <v>0.000593</v>
+        <v>5.9299999999999999E-4</v>
       </c>
       <c r="H2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7903,13 +7964,13 @@
         <v>56</v>
       </c>
       <c r="G3">
-        <v>0.000155</v>
+        <v>1.55E-4</v>
       </c>
       <c r="H3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7929,13 +7990,13 @@
         <v>56</v>
       </c>
       <c r="G4">
-        <v>0.000123</v>
+        <v>1.2300000000000001E-4</v>
       </c>
       <c r="H4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -7955,13 +8016,13 @@
         <v>56</v>
       </c>
       <c r="G5">
-        <v>0.000131</v>
+        <v>1.3100000000000001E-4</v>
       </c>
       <c r="H5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -7981,13 +8042,13 @@
         <v>56</v>
       </c>
       <c r="G6">
-        <v>0.000116</v>
+        <v>1.16E-4</v>
       </c>
       <c r="H6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -8007,13 +8068,13 @@
         <v>56</v>
       </c>
       <c r="G7">
-        <v>0.000114</v>
+        <v>1.1400000000000001E-4</v>
       </c>
       <c r="H7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -8033,13 +8094,13 @@
         <v>56</v>
       </c>
       <c r="G8">
-        <v>0.00012</v>
+        <v>1.2E-4</v>
       </c>
       <c r="H8" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -8059,7 +8120,7 @@
         <v>56</v>
       </c>
       <c r="G9">
-        <v>0.000117</v>
+        <v>1.17E-4</v>
       </c>
       <c r="H9" t="s">
         <v>57</v>
@@ -8067,6 +8128,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>